--- a/Impostos_Retidos_Recolhidos_GDF/Resumo_Impostos_por_ano-2012-2026.xlsx
+++ b/Impostos_Retidos_Recolhidos_GDF/Resumo_Impostos_por_ano-2012-2026.xlsx
@@ -24,7 +24,10 @@
     <t>Extração Impostos</t>
   </si>
   <si>
-    <t>Posição 14/09/2026 - 08h</t>
+    <t>Série Histórica 2012 a 2026</t>
+  </si>
+  <si>
+    <t>Posição 14/09/2026 - 14h</t>
   </si>
   <si>
     <t>ANO_EXERCICIO</t>
@@ -112,18 +115,12 @@
   </si>
   <si>
     <t>Total Geral</t>
-  </si>
-  <si>
-    <t>Série Histórica 2012 a 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
   <fonts count="6">
     <font>
       <sz val="11"/>
@@ -202,28 +199,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -546,1108 +539,1108 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="18.75">
-      <c r="A1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
+      <c r="A1" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
+      <c r="A2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
+      <c r="A3" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3">
+        <v>572500.03000000014</v>
+      </c>
+      <c r="D6" s="3">
+        <v>921454.92000000016</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7">
-        <v>831570.76000000013</v>
-      </c>
-      <c r="D6" s="7">
-        <v>54072.32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="8">
+      <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
         <v>4039268.93</v>
       </c>
-      <c r="D7" s="8">
-        <v>546975.78</v>
+      <c r="D7" s="5">
+        <v>6039645.7899999991</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>321.20999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>301.57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="8">
-        <v>1240368.909999999</v>
-      </c>
-      <c r="D9" s="8">
-        <v>187858.64</v>
+      <c r="B9" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="5">
+        <v>973497.85999999987</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1717108.86</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="C10" s="3">
         <v>5229502.72</v>
       </c>
-      <c r="D10" s="7">
-        <v>845061.61</v>
+      <c r="D10" s="3">
+        <v>9278348.3699999992</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="8">
-        <v>0</v>
-      </c>
-      <c r="D11" s="8">
-        <v>11558.19</v>
+      <c r="B11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>39000.33</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="7">
-        <v>382546718.07000011</v>
-      </c>
-      <c r="D12" s="7">
-        <v>35592929.869999997</v>
+        <v>8</v>
+      </c>
+      <c r="C12" s="3">
+        <v>353303739.88000011</v>
+      </c>
+      <c r="D12" s="3">
+        <v>943990706.02999902</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="8">
-        <v>101620045.67</v>
-      </c>
-      <c r="D13" s="8">
-        <v>14014571.17</v>
+      <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>63708911.499999978</v>
+      </c>
+      <c r="D13" s="5">
+        <v>127721897.11</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="7">
-        <v>38.979999999999997</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <v>10999.57</v>
+      <c r="C15" s="5">
+        <v>0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>31831.65</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1514910331.4100001</v>
-      </c>
-      <c r="D16" s="7">
-        <v>173888522.09000009</v>
+        <v>8</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1165476028.6700001</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2312880408.8800001</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="8">
-        <v>70475100.409999996</v>
-      </c>
-      <c r="D17" s="8">
-        <v>9825512.1900000013</v>
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="5">
+        <v>58557009.529999979</v>
+      </c>
+      <c r="D17" s="5">
+        <v>126730997</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7">
-        <v>21366.18</v>
+        <v>13</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>42732.36</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="8">
-        <v>550695272.94000006</v>
-      </c>
-      <c r="D19" s="8">
-        <v>141589639.05000001</v>
+      <c r="A19" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>433265883.94000012</v>
+      </c>
+      <c r="D19" s="5">
+        <v>2271497733.749999</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>72723061.260000005</v>
-      </c>
-      <c r="D20" s="7">
-        <v>11830383.73</v>
+        <v>9</v>
+      </c>
+      <c r="C20" s="3">
+        <v>64139027.880000003</v>
+      </c>
+      <c r="D20" s="3">
+        <v>130720098.95000011</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C21" s="8">
-        <v>0</v>
-      </c>
-      <c r="D21" s="8">
-        <v>0</v>
+      <c r="A21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0</v>
+      </c>
+      <c r="D21" s="5">
+        <v>24351.01</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="7">
-        <v>1256810619.069999</v>
-      </c>
-      <c r="D22" s="7">
-        <v>194765274.50999999</v>
+        <v>8</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1019754913.95</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1954398561.24</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="8">
-        <v>74404198.169999972</v>
-      </c>
-      <c r="D23" s="8">
-        <v>11868238.869999999</v>
+      <c r="A23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="5">
+        <v>63498697.130000032</v>
+      </c>
+      <c r="D23" s="5">
+        <v>133781417.04000001</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
+        <v>11</v>
+      </c>
+      <c r="C24" s="3">
         <v>211.34</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C25" s="8">
-        <v>0</v>
-      </c>
-      <c r="D25" s="8">
-        <v>45766.97</v>
+      <c r="A25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+      <c r="D25" s="5">
+        <v>92444.86</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="7">
-        <v>1467451676.059999</v>
-      </c>
-      <c r="D26" s="7">
-        <v>117015945.45</v>
+        <v>8</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1405987731.6999991</v>
+      </c>
+      <c r="D26" s="3">
+        <v>2183331113.2599978</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="8">
-        <v>90215345.039999992</v>
-      </c>
-      <c r="D27" s="8">
-        <v>16254169.859999999</v>
+      <c r="A27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="5">
+        <v>72344481.13000004</v>
+      </c>
+      <c r="D27" s="5">
+        <v>158044225.20999989</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="7">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3">
         <v>2381.7199999999998</v>
       </c>
-      <c r="D28" s="7">
-        <v>0</v>
+      <c r="D28" s="3">
+        <v>79821.83</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="8">
-        <v>0</v>
-      </c>
-      <c r="D29" s="8">
-        <v>0</v>
+      <c r="A29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="D29" s="5">
+        <v>50374.02</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="7">
-        <v>1306568200.0799999</v>
-      </c>
-      <c r="D30" s="7">
-        <v>94118590.530000001</v>
+        <v>8</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1194747584.8900011</v>
+      </c>
+      <c r="D30" s="3">
+        <v>1829978834.3400011</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="8">
-        <v>76180182.330000013</v>
-      </c>
-      <c r="D31" s="8">
-        <v>7235942.9700000035</v>
+      <c r="A31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="5">
+        <v>67415732.090000033</v>
+      </c>
+      <c r="D31" s="5">
+        <v>146131753.12</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="7">
-        <v>0</v>
-      </c>
-      <c r="D32" s="7">
-        <v>0</v>
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2289.59</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="8">
-        <v>0</v>
-      </c>
-      <c r="D33" s="8">
-        <v>72062.8</v>
+      <c r="A33" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0</v>
+      </c>
+      <c r="D33" s="5">
+        <v>125010.02</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="7">
-        <v>1289205269.52</v>
-      </c>
-      <c r="D34" s="7">
-        <v>107863436.67</v>
+        <v>8</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1111557824.279999</v>
+      </c>
+      <c r="D34" s="3">
+        <v>2016352917.7700009</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="8">
-        <v>79435570.169999987</v>
-      </c>
-      <c r="D35" s="8">
-        <v>12359425.01</v>
+      <c r="A35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="5">
+        <v>73217337.259999961</v>
+      </c>
+      <c r="D35" s="5">
+        <v>159519789.22999999</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="7">
-        <v>0</v>
-      </c>
-      <c r="D36" s="7">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3">
+        <v>51055.01</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="8">
-        <v>1487600504.23</v>
-      </c>
-      <c r="D37" s="8">
-        <v>122687300.2</v>
+      <c r="A37" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="5">
+        <v>1227007877.74</v>
+      </c>
+      <c r="D37" s="5">
+        <v>1812565543.1000011</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="7">
-        <v>103679864.79000001</v>
-      </c>
-      <c r="D38" s="7">
-        <v>13590994.40000001</v>
+        <v>9</v>
+      </c>
+      <c r="C38" s="3">
+        <v>91754078.01000005</v>
+      </c>
+      <c r="D38" s="3">
+        <v>177017509.57000011</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="8">
-        <v>0</v>
-      </c>
-      <c r="D39" s="8">
-        <v>5908.89</v>
+      <c r="A39" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="5">
+        <v>0</v>
+      </c>
+      <c r="D39" s="5">
+        <v>50907.73</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7">
-        <v>21225.5</v>
-      </c>
-      <c r="D40" s="7">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="C40" s="3">
+        <v>20398.86</v>
+      </c>
+      <c r="D40" s="3">
+        <v>7978.72</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="8">
-        <v>0</v>
-      </c>
-      <c r="D41" s="8">
-        <v>49908.92</v>
+      <c r="A41" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C41" s="5">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5">
+        <v>241962.32</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1619769955.470001</v>
-      </c>
-      <c r="D42" s="7">
-        <v>97831122.489999995</v>
+        <v>8</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1477264033.23</v>
+      </c>
+      <c r="D42" s="3">
+        <v>2124412624.069998</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="8">
-        <v>106111884.23999999</v>
-      </c>
-      <c r="D43" s="8">
-        <v>16915912.409999989</v>
+      <c r="A43" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="5">
+        <v>95026355.549999952</v>
+      </c>
+      <c r="D43" s="5">
+        <v>209130274.30999979</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C44" s="7">
-        <v>0</v>
-      </c>
-      <c r="D44" s="7">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="C44" s="3">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3">
+        <v>15632.66</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="8">
-        <v>7126.57</v>
-      </c>
-      <c r="D45" s="8">
-        <v>0</v>
+      <c r="A45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="5">
+        <v>6370.5800000000008</v>
+      </c>
+      <c r="D45" s="5">
+        <v>18004.669999999998</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C46" s="7">
-        <v>0</v>
-      </c>
-      <c r="D46" s="7">
-        <v>108488.43</v>
+        <v>13</v>
+      </c>
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
+        <v>297340.79999999999</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="8">
-        <v>1089737152.6500001</v>
-      </c>
-      <c r="D47" s="8">
-        <v>232799559.71000001</v>
+      <c r="A47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="5">
+        <v>966490124.84000003</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2048173713.259999</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="7">
-        <v>107265562.76999991</v>
-      </c>
-      <c r="D48" s="7">
-        <v>6561064.9199999999</v>
+        <v>9</v>
+      </c>
+      <c r="C48" s="3">
+        <v>98914582.669999957</v>
+      </c>
+      <c r="D48" s="3">
+        <v>192405291.20000011</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="8">
-        <v>0</v>
-      </c>
-      <c r="D49" s="8">
-        <v>0</v>
+      <c r="A49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="5">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5">
+        <v>16011.09</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="7">
-        <v>0</v>
-      </c>
-      <c r="D50" s="7">
-        <v>3750.46</v>
+        <v>13</v>
+      </c>
+      <c r="C50" s="3">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3">
+        <v>307864.53999999998</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="8">
-        <v>1510021308.5899999</v>
-      </c>
-      <c r="D51" s="8">
-        <v>143807087.16</v>
+      <c r="A51" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="5">
+        <v>1324081640.3399999</v>
+      </c>
+      <c r="D51" s="5">
+        <v>2491169522.4599962</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="7">
-        <v>135803365.63</v>
-      </c>
-      <c r="D52" s="7">
-        <v>10545427.279999999</v>
+        <v>9</v>
+      </c>
+      <c r="C52" s="3">
+        <v>120486692.20999999</v>
+      </c>
+      <c r="D52" s="3">
+        <v>244828106.22999999</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="8">
-        <v>0</v>
-      </c>
-      <c r="D53" s="8">
-        <v>743.75</v>
+      <c r="A53" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="5">
+        <v>0</v>
+      </c>
+      <c r="D53" s="5">
+        <v>12067.43</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="7">
-        <v>0</v>
-      </c>
-      <c r="D54" s="7">
+        <v>11</v>
+      </c>
+      <c r="C54" s="3">
+        <v>-552.4</v>
+      </c>
+      <c r="D54" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="8">
-        <v>0</v>
-      </c>
-      <c r="D55" s="8">
-        <v>179123.22</v>
+      <c r="A55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="5">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5">
+        <v>429292.79</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="7">
-        <v>2002399758.3500011</v>
-      </c>
-      <c r="D56" s="7">
-        <v>100613597.40000001</v>
+        <v>8</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1951654943.04</v>
+      </c>
+      <c r="D56" s="3">
+        <v>2747595400.8800001</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C57" s="8">
-        <v>152193596.57999989</v>
-      </c>
-      <c r="D57" s="8">
-        <v>16373290.29000001</v>
+      <c r="A57" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="5">
+        <v>143409552.0699999</v>
+      </c>
+      <c r="D57" s="5">
+        <v>294814634.49999988</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1385.87</v>
-      </c>
-      <c r="D58" s="7">
+        <v>11</v>
+      </c>
+      <c r="C58" s="3">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="8">
-        <v>0</v>
-      </c>
-      <c r="D59" s="8">
-        <v>53858.15</v>
+      <c r="A59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C59" s="5">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5">
+        <v>265936.31</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1266392480.6300001</v>
-      </c>
-      <c r="D60" s="7">
-        <v>128729086.91</v>
+        <v>8</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1182004281.25</v>
+      </c>
+      <c r="D60" s="3">
+        <v>2080610841.599999</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C61" s="8">
-        <v>110951002.73999991</v>
-      </c>
-      <c r="D61" s="8">
-        <v>11437664.58</v>
+      <c r="A61" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="5">
+        <v>104343031.28</v>
+      </c>
+      <c r="D61" s="5">
+        <v>212909063.04000011</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B62" s="14"/>
-      <c r="C62" s="9">
-        <v>18036541108.17001</v>
-      </c>
-      <c r="D62" s="9">
-        <v>1852312495.170001</v>
+      <c r="A62" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B62" s="12"/>
+      <c r="C62" s="6">
+        <v>15940255675.700001</v>
+      </c>
+      <c r="D62" s="6">
+        <v>29150871766.039989</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="10" t="s">
+      <c r="A65" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="B65" s="7"/>
+      <c r="C65" s="7" t="s">
         <v>29</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>10</v>
-      </c>
-      <c r="C66" s="11">
-        <v>29988.26</v>
-      </c>
-      <c r="D66" s="11">
-        <v>301.57</v>
+        <v>11</v>
+      </c>
+      <c r="C66" s="8">
+        <v>26428.38</v>
+      </c>
+      <c r="D66" s="8">
+        <v>26304.6</v>
       </c>
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>12</v>
-      </c>
-      <c r="C67" s="11">
-        <v>0</v>
-      </c>
-      <c r="D67" s="11">
-        <v>556882.89</v>
+        <v>13</v>
+      </c>
+      <c r="C67" s="8">
+        <v>0</v>
+      </c>
+      <c r="D67" s="8">
+        <v>1999196.02</v>
       </c>
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="11">
-        <v>16746181186.74</v>
-      </c>
-      <c r="D68" s="11">
-        <v>1691544023</v>
+        <v>8</v>
+      </c>
+      <c r="C68" s="8">
+        <v>14814142605.639999</v>
+      </c>
+      <c r="D68" s="8">
+        <v>26819596484.419991</v>
       </c>
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>8</v>
-      </c>
-      <c r="C69" s="11">
-        <v>1290327551.45</v>
-      </c>
-      <c r="D69" s="11">
-        <v>160204635.06999999</v>
+        <v>9</v>
+      </c>
+      <c r="C69" s="8">
+        <v>1126084259.96</v>
+      </c>
+      <c r="D69" s="8">
+        <v>2329073050.6700001</v>
       </c>
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>17</v>
-      </c>
-      <c r="C70" s="11">
+        <v>18</v>
+      </c>
+      <c r="C70" s="8">
         <v>2381.7199999999998</v>
       </c>
-      <c r="D70" s="11">
-        <v>6652.64</v>
+      <c r="D70" s="8">
+        <v>176730.33</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" s="10">
+        <v>15940255675.700001</v>
+      </c>
+      <c r="D71" s="10">
+        <v>29150871766.039989</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" s="7"/>
+      <c r="C74" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>30</v>
-      </c>
-      <c r="C71" s="12">
-        <v>18036541108.17001</v>
-      </c>
-      <c r="D71" s="12">
-        <v>1852312495.170001</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="11">
-        <v>4870839.6899999985</v>
-      </c>
-      <c r="D75" s="11">
-        <v>601048.1</v>
+        <v>7</v>
+      </c>
+      <c r="C75" s="8">
+        <v>4611768.96</v>
+      </c>
+      <c r="D75" s="8">
+        <v>6961100.709999999</v>
       </c>
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" s="11">
-        <v>6469871.629999999</v>
-      </c>
-      <c r="D76" s="11">
-        <v>1033221.82</v>
+        <v>10</v>
+      </c>
+      <c r="C76" s="8">
+        <v>6203000.5800000001</v>
+      </c>
+      <c r="D76" s="8">
+        <v>10995778.439999999</v>
       </c>
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="11">
-        <v>484166763.74000013</v>
-      </c>
-      <c r="D77" s="11">
-        <v>49619059.229999997</v>
+        <v>12</v>
+      </c>
+      <c r="C77" s="8">
+        <v>417012651.38000011</v>
+      </c>
+      <c r="D77" s="8">
+        <v>1071751603.469999</v>
       </c>
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>13</v>
-      </c>
-      <c r="C78" s="11">
-        <v>1585385470.8</v>
-      </c>
-      <c r="D78" s="11">
-        <v>183725033.85000011</v>
+        <v>14</v>
+      </c>
+      <c r="C78" s="8">
+        <v>1224033038.2</v>
+      </c>
+      <c r="D78" s="8">
+        <v>2439643237.5300002</v>
       </c>
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>14</v>
-      </c>
-      <c r="C79" s="11">
-        <v>623418334.20000005</v>
-      </c>
-      <c r="D79" s="11">
-        <v>153441388.96000001</v>
+        <v>15</v>
+      </c>
+      <c r="C79" s="8">
+        <v>497404911.82000011</v>
+      </c>
+      <c r="D79" s="8">
+        <v>2402260565.059999</v>
       </c>
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="C80" s="11">
-        <v>1331214817.24</v>
-      </c>
-      <c r="D80" s="11">
-        <v>206633513.38</v>
+        <v>16</v>
+      </c>
+      <c r="C80" s="8">
+        <v>1083253611.0799999</v>
+      </c>
+      <c r="D80" s="8">
+        <v>2088204329.29</v>
       </c>
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" s="11">
-        <v>1557669614.1599989</v>
-      </c>
-      <c r="D81" s="11">
-        <v>133315882.28</v>
+        <v>17</v>
+      </c>
+      <c r="C81" s="8">
+        <v>1478334805.8899989</v>
+      </c>
+      <c r="D81" s="8">
+        <v>2341547605.1599979</v>
       </c>
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>18</v>
-      </c>
-      <c r="C82" s="11">
-        <v>1382748382.4100001</v>
-      </c>
-      <c r="D82" s="11">
-        <v>101354533.5</v>
+        <v>19</v>
+      </c>
+      <c r="C82" s="8">
+        <v>1262163316.98</v>
+      </c>
+      <c r="D82" s="8">
+        <v>1976163251.0700009</v>
       </c>
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>19</v>
-      </c>
-      <c r="C83" s="11">
-        <v>1368640839.6900001</v>
-      </c>
-      <c r="D83" s="11">
-        <v>120294924.48</v>
+        <v>20</v>
+      </c>
+      <c r="C83" s="8">
+        <v>1184775161.539999</v>
+      </c>
+      <c r="D83" s="8">
+        <v>2175997717.0200009</v>
       </c>
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>20</v>
-      </c>
-      <c r="C84" s="11">
-        <v>1591280369.02</v>
-      </c>
-      <c r="D84" s="11">
-        <v>136284203.49000001</v>
+        <v>21</v>
+      </c>
+      <c r="C84" s="8">
+        <v>1318761955.75</v>
+      </c>
+      <c r="D84" s="8">
+        <v>1989685015.410001</v>
       </c>
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>21</v>
-      </c>
-      <c r="C85" s="11">
-        <v>1725903065.210001</v>
-      </c>
-      <c r="D85" s="11">
-        <v>114796943.81999999</v>
+        <v>22</v>
+      </c>
+      <c r="C85" s="8">
+        <v>1572310787.6400001</v>
+      </c>
+      <c r="D85" s="8">
+        <v>2333808472.079998</v>
       </c>
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>22</v>
-      </c>
-      <c r="C86" s="11">
-        <v>1197009841.99</v>
-      </c>
-      <c r="D86" s="11">
-        <v>239469113.06</v>
+        <v>23</v>
+      </c>
+      <c r="C86" s="8">
+        <v>1065411078.09</v>
+      </c>
+      <c r="D86" s="8">
+        <v>2240910361.02</v>
       </c>
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>23</v>
-      </c>
-      <c r="C87" s="11">
-        <v>1645824674.22</v>
-      </c>
-      <c r="D87" s="11">
-        <v>154357008.65000001</v>
+        <v>24</v>
+      </c>
+      <c r="C87" s="8">
+        <v>1444568332.55</v>
+      </c>
+      <c r="D87" s="8">
+        <v>2736317560.659996</v>
       </c>
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>24</v>
-      </c>
-      <c r="C88" s="11">
-        <v>2154593354.9299998</v>
-      </c>
-      <c r="D88" s="11">
-        <v>117166010.91</v>
+        <v>25</v>
+      </c>
+      <c r="C88" s="8">
+        <v>2095063942.71</v>
+      </c>
+      <c r="D88" s="8">
+        <v>3042839328.1700001</v>
       </c>
     </row>
     <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>25</v>
-      </c>
-      <c r="C89" s="11">
-        <v>1377344869.24</v>
-      </c>
-      <c r="D89" s="11">
-        <v>140220609.63999999</v>
+        <v>26</v>
+      </c>
+      <c r="C89" s="8">
+        <v>1286347312.53</v>
+      </c>
+      <c r="D89" s="8">
+        <v>2293785840.9499989</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C90" s="12">
-        <v>18036541108.17001</v>
-      </c>
-      <c r="D90" s="12">
-        <v>1852312495.170001</v>
+      <c r="A90" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="10">
+        <v>15940255675.700001</v>
+      </c>
+      <c r="D90" s="10">
+        <v>29150871766.039989</v>
       </c>
     </row>
   </sheetData>
